--- a/output/2024_estado_nutricional_por_SS.xlsx
+++ b/output/2024_estado_nutricional_por_SS.xlsx
@@ -303,7 +303,7 @@
     <t>Servicio de Salud Metropolitano Sur</t>
   </si>
   <si>
-    <t>Servicio de Salud Metropolitano Sur Oriente</t>
+    <t>Servicio de Salud Metropolitano Sur - Oriente</t>
   </si>
 </sst>
 </file>
